--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -17576,7 +17576,7 @@
         <v>79106848</v>
       </c>
       <c r="B158" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -17605,11 +17605,7 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>

--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -17576,7 +17576,7 @@
         <v>79106848</v>
       </c>
       <c r="B158" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
